--- a/apps/api/templates/waybill-4p.xlsx
+++ b/apps/api/templates/waybill-4p.xlsx
@@ -1253,7 +1253,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="233">
+  <cellXfs count="241">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1941,6 +1941,30 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="49" xfId="0" applyBorder="1" applyAlignment="true">
+      <alignment shrinkToFit="true" horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="true">
+      <alignment shrinkToFit="true" horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="true">
+      <alignment shrinkToFit="true" horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="true">
+      <alignment shrinkToFit="true" horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="49" xfId="0" applyBorder="1" applyAlignment="true">
+      <alignment shrinkToFit="true" horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="true">
+      <alignment shrinkToFit="true" horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="true">
+      <alignment shrinkToFit="true" horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="true">
+      <alignment shrinkToFit="true" horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="true">
       <alignment wrapText="true" horizontal="left" vertical="top"/>
@@ -12014,7 +12038,7 @@
       <c r="CB76" s="207"/>
       <c r="CC76" s="207"/>
       <c r="CD76" s="207"/>
-      <c r="CG76" s="230" t="inlineStr">
+      <c r="CG76" s="238" t="inlineStr">
         <is>
           <t xml:space="preserve">{{task5_line}}</t>
         </is>
@@ -12196,7 +12220,7 @@
       <c r="CB77" s="207"/>
       <c r="CC77" s="207"/>
       <c r="CD77" s="207"/>
-      <c r="CG77" s="231" t="inlineStr">
+      <c r="CG77" s="239" t="inlineStr">
         <is>
           <t xml:space="preserve">{{task6_line}}</t>
         </is>
@@ -12378,7 +12402,7 @@
       <c r="CB78" s="207"/>
       <c r="CC78" s="207"/>
       <c r="CD78" s="207"/>
-      <c r="CG78" s="232" t="inlineStr">
+      <c r="CG78" s="240" t="inlineStr">
         <is>
           <t xml:space="preserve">{{task7_line}}</t>
         </is>
@@ -15250,7 +15274,11 @@
       <c r="J96" s="213"/>
       <c r="K96" s="213"/>
       <c r="L96" s="213"/>
-      <c r="M96" s="214"/>
+      <c r="M96" s="230" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{{org_name}}</t>
+        </is>
+      </c>
       <c r="N96" s="214"/>
       <c r="O96" s="214"/>
       <c r="P96" s="214"/>
@@ -15334,7 +15362,11 @@
       <c r="CP96" s="213"/>
       <c r="CQ96" s="213"/>
       <c r="CR96" s="213"/>
-      <c r="CS96" s="214"/>
+      <c r="CS96" s="234" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{{org_name}}</t>
+        </is>
+      </c>
       <c r="CT96" s="214"/>
       <c r="CU96" s="214"/>
       <c r="CV96" s="214"/>
@@ -15425,7 +15457,11 @@
       <c r="O97" s="215"/>
       <c r="P97" s="215"/>
       <c r="Q97" s="215"/>
-      <c r="R97" s="88"/>
+      <c r="R97" s="231" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{{vehicle_brand}}</t>
+        </is>
+      </c>
       <c r="S97" s="88"/>
       <c r="T97" s="88"/>
       <c r="U97" s="88"/>
@@ -15475,7 +15511,11 @@
       <c r="BK97" s="74"/>
       <c r="BL97" s="74"/>
       <c r="BM97" s="74"/>
-      <c r="BN97" s="88"/>
+      <c r="BN97" s="88" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{{vehicle_reg_number}}</t>
+        </is>
+      </c>
       <c r="BO97" s="88"/>
       <c r="BP97" s="88"/>
       <c r="BQ97" s="88"/>
@@ -15511,7 +15551,11 @@
       <c r="CU97" s="215"/>
       <c r="CV97" s="215"/>
       <c r="CW97" s="215"/>
-      <c r="CX97" s="88"/>
+      <c r="CX97" s="235" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{{vehicle_brand}}</t>
+        </is>
+      </c>
       <c r="CY97" s="88"/>
       <c r="CZ97" s="88"/>
       <c r="DA97" s="88"/>
@@ -15561,7 +15605,11 @@
       <c r="EQ97" s="74"/>
       <c r="ER97" s="74"/>
       <c r="ES97" s="74"/>
-      <c r="ET97" s="88"/>
+      <c r="ET97" s="88" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{{vehicle_reg_number}}</t>
+        </is>
+      </c>
       <c r="EU97" s="88"/>
       <c r="EV97" s="88"/>
       <c r="EW97" s="88"/>
@@ -15591,7 +15639,11 @@
       <c r="G98" s="215"/>
       <c r="H98" s="215"/>
       <c r="I98" s="215"/>
-      <c r="R98" s="100"/>
+      <c r="R98" s="232" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{{trailers_brands}}</t>
+        </is>
+      </c>
       <c r="S98" s="100"/>
       <c r="T98" s="100"/>
       <c r="U98" s="100"/>
@@ -15641,7 +15693,11 @@
       <c r="BK98" s="74"/>
       <c r="BL98" s="74"/>
       <c r="BM98" s="74"/>
-      <c r="BN98" s="100"/>
+      <c r="BN98" s="233" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{{trailers_reg_numbers}}</t>
+        </is>
+      </c>
       <c r="BO98" s="100"/>
       <c r="BP98" s="100"/>
       <c r="BQ98" s="100"/>
@@ -15669,7 +15725,11 @@
       <c r="CM98" s="215"/>
       <c r="CN98" s="215"/>
       <c r="CO98" s="215"/>
-      <c r="CX98" s="100"/>
+      <c r="CX98" s="236" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{{trailers_brands}}</t>
+        </is>
+      </c>
       <c r="CY98" s="100"/>
       <c r="CZ98" s="100"/>
       <c r="DA98" s="100"/>
@@ -15719,7 +15779,11 @@
       <c r="EQ98" s="74"/>
       <c r="ER98" s="74"/>
       <c r="ES98" s="74"/>
-      <c r="ET98" s="100"/>
+      <c r="ET98" s="237" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{{trailers_reg_numbers}}</t>
+        </is>
+      </c>
       <c r="EU98" s="100"/>
       <c r="EV98" s="100"/>
       <c r="EW98" s="100"/>
